--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484122_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484122_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5199</v>
+        <v>7.6893</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7882</v>
+        <v>2.7712</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7317</v>
+        <v>4.9181</v>
       </c>
       <c r="G2" t="n">
         <v>4.4769</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0511</v>
+        <v>2.2204</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3661</v>
+        <v>1.3491</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6849</v>
+        <v>0.8713</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.46</v>
+        <v>5.4483</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3379</v>
+        <v>1.9694</v>
       </c>
       <c r="F3" t="n">
-        <v>1.122</v>
+        <v>3.4789</v>
       </c>
       <c r="G3" t="n">
-        <v>6.0984</v>
+        <v>5.3582</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9648</v>
+        <v>2.6959</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1336</v>
+        <v>2.6623</v>
       </c>
       <c r="J3" t="n">
-        <v>5.4448</v>
+        <v>3.1539</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8748</v>
+        <v>1.4569</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5699</v>
+        <v>1.697</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6536999999999999</v>
+        <v>2.2043</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09</v>
+        <v>1.239</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5637</v>
+        <v>0.9653</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.1741</v>
+        <v>0.1984</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.158</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9324</v>
+        <v>1.0982</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2414</v>
+        <v>0.7993</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.309</v>
+        <v>0.2989</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6032</v>
+        <v>-1.2065</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-1.2065</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2713</v>
+        <v>4.5577</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9888</v>
+        <v>3.0148</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2825</v>
+        <v>1.5429</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3582</v>
+        <v>6.0984</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6959</v>
+        <v>4.9648</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6623</v>
+        <v>1.1336</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1539</v>
+        <v>5.4448</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4569</v>
+        <v>4.8748</v>
       </c>
       <c r="L4" t="n">
-        <v>1.697</v>
+        <v>0.5699</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2043</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>1.239</v>
+        <v>0.09</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9653</v>
+        <v>0.5637</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-5.158</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0788</v>
+        <v>1.0302</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1813</v>
+        <v>0.9183</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1025</v>
+        <v>0.1118</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2065</v>
+        <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X4" t="n">
         <v>-1.2065</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1954</v>
+        <v>1.7273</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1795</v>
+        <v>0.7114</v>
       </c>
       <c r="F5" t="n">
         <v>1.0159</v>
@@ -844,10 +844,10 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2195</v>
+        <v>1.7514</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8399</v>
+        <v>1.3718</v>
       </c>
       <c r="U5" t="n">
         <v>0.3797</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0945</v>
+        <v>0.2492</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4269</v>
+        <v>-2.6127</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5214</v>
+        <v>2.8619</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5573</v>
+        <v>0.2032</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2375</v>
+        <v>1.3964</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6802</v>
+        <v>-1.1932</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9801</v>
+        <v>-0.1095</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9801</v>
+        <v>0.5656</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6751</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4228</v>
+        <v>0.3127</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2574</v>
+        <v>0.8309</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6802</v>
+        <v>-0.5182</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3307</v>
+        <v>1.6962</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5532</v>
+        <v>1.2698</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7776</v>
+        <v>0.4264</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8692</v>
+        <v>0.532</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8692</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2522</v>
+        <v>-0.148</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3059</v>
+        <v>-1.2205</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5581</v>
+        <v>1.0725</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5590000000000001</v>
+        <v>-1.5573</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1509</v>
+        <v>-2.2375</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4081</v>
+        <v>0.6802</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0128</v>
+        <v>-1.9801</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1358</v>
+        <v>-1.9801</v>
       </c>
       <c r="L7" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5718</v>
+        <v>0.4228</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2867</v>
+        <v>-0.2574</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2851</v>
+        <v>0.6802</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0818</v>
+        <v>1.0883</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6746</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4072</v>
+        <v>0.3287</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6032</v>
+        <v>-0.8692</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8097</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1677</v>
+        <v>-0.2185</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7771</v>
+        <v>-1.2435</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6094</v>
+        <v>1.025</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2032</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3964</v>
+        <v>0.1509</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1932</v>
+        <v>0.4081</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1095</v>
+        <v>-0.0128</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5656</v>
+        <v>-0.1358</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6751</v>
+        <v>0.123</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3127</v>
+        <v>0.5718</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8309</v>
+        <v>0.2867</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5182</v>
+        <v>0.2851</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1822</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9677</v>
+        <v>-3.1741</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2793</v>
+        <v>1.6111</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1054</v>
+        <v>0.7369</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1739</v>
+        <v>0.8742</v>
       </c>
       <c r="V8" t="n">
-        <v>0.532</v>
+        <v>-0.6032</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1947</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3373</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2661</v>
+        <v>-0.3648</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3485</v>
+        <v>-0.4845</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6146</v>
+        <v>0.1197</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4547</v>
+        <v>-3.3472</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9623</v>
+        <v>0.1664</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4925</v>
+        <v>-3.5136</v>
       </c>
       <c r="J9" t="n">
-        <v>0.278</v>
+        <v>-1.5668</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3672</v>
+        <v>0.3533</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6451</v>
+        <v>-1.9201</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7327</v>
+        <v>-1.7804</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5951</v>
+        <v>-0.187</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1376</v>
+        <v>-1.5935</v>
       </c>
       <c r="P9" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-0.1984</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.1903</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0615</v>
+        <v>1.3277</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7289</v>
+        <v>1.0147</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3327</v>
+        <v>0.3131</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>0.532</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6794</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5879</v>
+        <v>-1.9531</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9085</v>
+        <v>1.2732</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1469</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0788</v>
+        <v>1.0784</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1814</v>
+        <v>0.8163</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1026</v>
+        <v>0.2621</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1239</v>
+        <v>-0.9483</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7307</v>
+        <v>0.1082</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3932</v>
+        <v>-1.0566</v>
       </c>
       <c r="G11" t="n">
         <v>0.2403</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0488</v>
+        <v>1.2243</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1928</v>
+        <v>1.0317</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.144</v>
+        <v>0.1926</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4129</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1307</v>
+        <v>-1.6399</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9979</v>
+        <v>1.0027</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1328</v>
+        <v>-2.6426</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3472</v>
+        <v>-2.4547</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1664</v>
+        <v>-0.9623</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.5136</v>
+        <v>-1.4925</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5668</v>
+        <v>0.278</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3533</v>
+        <v>-0.3672</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9201</v>
+        <v>0.6451</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7804</v>
+        <v>-2.7327</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.187</v>
+        <v>-0.5951</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5935</v>
+        <v>-2.1376</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4382</v>
+        <v>1.6877</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4988</v>
+        <v>1.3831</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0606</v>
+        <v>0.3046</v>
       </c>
       <c r="V12" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="W12" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.4255</v>
+        <v>15.6724</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8164999999999991</v>
+        <v>2.0634</v>
       </c>
       <c r="F13" t="n">
         <v>13.6089</v>
       </c>
       <c r="G13" t="n">
-        <v>7.679799999999998</v>
+        <v>7.679799999999999</v>
       </c>
       <c r="H13" t="n">
         <v>9.0726</v>
@@ -1441,10 +1441,10 @@
         <v>-1.3929</v>
       </c>
       <c r="J13" t="n">
-        <v>5.593100000000001</v>
+        <v>5.593100000000002</v>
       </c>
       <c r="K13" t="n">
-        <v>5.172799999999998</v>
+        <v>5.172799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>0.4201000000000004</v>
@@ -1468,22 +1468,22 @@
         <v>16.8626</v>
       </c>
       <c r="S13" t="n">
-        <v>14.5669</v>
+        <v>15.8139</v>
       </c>
       <c r="T13" t="n">
-        <v>10.2036</v>
+        <v>11.4506</v>
       </c>
       <c r="U13" t="n">
-        <v>4.3635</v>
+        <v>4.3634</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.837499999999999</v>
+        <v>-5.8375</v>
       </c>
       <c r="W13" t="n">
-        <v>3.8664</v>
+        <v>3.866400000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.703899999999999</v>
+        <v>-9.703900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5572</v>
+        <v>5.0197</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3661</v>
+        <v>4.4681</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1911</v>
+        <v>0.5516</v>
       </c>
       <c r="G14" t="n">
         <v>5.7367</v>
@@ -1546,13 +1546,13 @@
         <v>2.1822</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8261</v>
+        <v>-2.3636</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.306</v>
+        <v>-0.2039</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.5202</v>
+        <v>-2.1597</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3373</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6599</v>
+        <v>2.3436</v>
       </c>
       <c r="E15" t="n">
-        <v>1.422</v>
+        <v>1.218</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2379</v>
+        <v>1.1257</v>
       </c>
       <c r="G15" t="n">
         <v>3.4149</v>
@@ -1624,13 +1624,13 @@
         <v>2.579</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1437</v>
+        <v>-2.46</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8784</v>
+        <v>-1.0825</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2653</v>
+        <v>-1.3775</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7277</v>
+        <v>1.1206</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6438</v>
+        <v>-0.3134</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9161</v>
+        <v>1.4339</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0576</v>
+        <v>-1.0736</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.2679</v>
+        <v>-0.2975</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2103</v>
+        <v>-0.7761</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0936</v>
+        <v>-0.1653</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9546</v>
+        <v>0.6303</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0482</v>
+        <v>-0.7956</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1512</v>
+        <v>-0.9083</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3132</v>
+        <v>-0.9278</v>
       </c>
       <c r="O16" t="n">
-        <v>0.162</v>
+        <v>0.0195</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.2309</v>
+        <v>-0.1431</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7481</v>
+        <v>-0.3626</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.4827</v>
+        <v>0.2196</v>
       </c>
       <c r="V16" t="n">
-        <v>3.6194</v>
+        <v>1.5437</v>
       </c>
       <c r="W16" t="n">
-        <v>4.4886</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8692</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.176</v>
+        <v>0.9317</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9255</v>
+        <v>2.8478</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1015</v>
+        <v>-1.9161</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0736</v>
+        <v>-0.0576</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2975</v>
+        <v>-2.2679</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7761</v>
+        <v>2.2103</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1653</v>
+        <v>0.0936</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6303</v>
+        <v>-1.9546</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7956</v>
+        <v>2.0482</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9083</v>
+        <v>-0.1512</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9278</v>
+        <v>-0.3132</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0195</v>
+        <v>0.162</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0877</v>
+        <v>-3.0268</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9748</v>
+        <v>-0.5441</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1129</v>
+        <v>-2.4827</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5437</v>
+        <v>3.6194</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2065</v>
+        <v>4.4886</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3373</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7164</v>
+        <v>-1.3721</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0583</v>
+        <v>0.1458</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6582</v>
+        <v>-1.5179</v>
       </c>
       <c r="G18" t="n">
         <v>0.865</v>
@@ -1858,13 +1858,13 @@
         <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.1884</v>
+        <v>-2.844</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4194</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.5649</v>
+        <v>-2.4246</v>
       </c>
       <c r="V18" t="n">
         <v>0.4085</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7909</v>
+        <v>-2.4508</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0429</v>
+        <v>-3.8388</v>
       </c>
       <c r="F19" t="n">
-        <v>1.252</v>
+        <v>1.388</v>
       </c>
       <c r="G19" t="n">
         <v>-4.3872</v>
@@ -1936,13 +1936,13 @@
         <v>2.3806</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4874</v>
+        <v>-0.1473</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7934</v>
+        <v>-0.5893</v>
       </c>
       <c r="U19" t="n">
-        <v>0.306</v>
+        <v>0.442</v>
       </c>
       <c r="V19" t="n">
         <v>2.6789</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1822</v>
+        <v>-3.8751</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.556</v>
+        <v>-5.9641</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3738</v>
+        <v>2.089</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8796</v>
@@ -2014,13 +2014,13 @@
         <v>2.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0571</v>
+        <v>-1.75</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3116</v>
+        <v>-0.7197</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7456</v>
+        <v>-1.0304</v>
       </c>
       <c r="V20" t="n">
         <v>1.1352</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.577</v>
+        <v>-4.008</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.031</v>
+        <v>-2.8401</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.546</v>
+        <v>-1.1679</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5881</v>
+        <v>-3.6829</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2396</v>
+        <v>-2.4495</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3485</v>
+        <v>-1.2334</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9372</v>
+        <v>-2.0353</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-1.3201</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>-0.7153</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6509</v>
+        <v>-1.6476</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2623</v>
+        <v>-1.1295</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3886</v>
+        <v>-0.5182</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4953</v>
+        <v>-0.7057</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5645</v>
+        <v>-0.8048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0692</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.0874</v>
+        <v>-1.2065</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3702</v>
+        <v>-4.5734</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1462</v>
+        <v>-3.0513</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.224</v>
+        <v>-1.5222</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.6829</v>
+        <v>-1.5881</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4495</v>
+        <v>-1.2396</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2334</v>
+        <v>-0.3485</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0353</v>
+        <v>-0.9372</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3201</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7153</v>
+        <v>0.0402</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6476</v>
+        <v>-0.6509</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1295</v>
+        <v>-0.2623</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5182</v>
+        <v>-0.3886</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5871</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0679</v>
+        <v>0.4988</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1109</v>
+        <v>0.5442</v>
       </c>
       <c r="U22" t="n">
-        <v>0.043</v>
+        <v>-0.0454</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2065</v>
+        <v>-3.0874</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9095</v>
+        <v>-6.8815</v>
       </c>
       <c r="E23" t="n">
         <v>-6.281</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.6005</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0274</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9732</v>
+        <v>-0.9452</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1813</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7919</v>
+        <v>-0.7639</v>
       </c>
       <c r="V23" t="n">
         <v>1.083</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.4254</v>
+        <v>-13.7453</v>
       </c>
       <c r="E24" t="n">
         <v>-13.609</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8164999999999997</v>
+        <v>-0.1364000000000003</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.6798</v>
+        <v>-7.679799999999999</v>
       </c>
       <c r="H24" t="n">
         <v>-9.072600000000001</v>
@@ -2299,7 +2299,7 @@
         <v>1.3928</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0868</v>
+        <v>-2.086800000000001</v>
       </c>
       <c r="K24" t="n">
         <v>-3.8997</v>
@@ -2326,22 +2326,22 @@
         <v>18.8466</v>
       </c>
       <c r="S24" t="n">
-        <v>-14.5671</v>
+        <v>-13.8869</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.3635</v>
+        <v>-4.3634</v>
       </c>
       <c r="U24" t="n">
-        <v>-10.2037</v>
+        <v>-9.5235</v>
       </c>
       <c r="V24" t="n">
         <v>5.8375</v>
       </c>
       <c r="W24" t="n">
-        <v>9.703900000000001</v>
+        <v>9.703899999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.8662</v>
+        <v>-3.866199999999999</v>
       </c>
     </row>
   </sheetData>
